--- a/实体 entity/生物分类.xlsx
+++ b/实体 entity/生物分类.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\常用\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\实体 entity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D104D6-5A8C-4779-8C9F-5C054BD4B56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCFF3E1-372D-49A1-AEF1-4EB16AE6584F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6312" yWindow="2832" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2890" yWindow="2270" windowWidth="19200" windowHeight="10050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,48 +38,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
   <si>
-    <t>MONSTER</t>
-  </si>
-  <si>
     <t>怪物</t>
   </si>
   <si>
-    <t>CREATURE</t>
-  </si>
-  <si>
     <t>动物</t>
   </si>
   <si>
-    <t>AMBIENT</t>
-  </si>
-  <si>
     <t>环境(蝙蝠)</t>
   </si>
   <si>
-    <t>AXOLOTLS</t>
-  </si>
-  <si>
     <t>美西螈</t>
   </si>
   <si>
-    <t>UNDERGROUND_WATER_CREATURE</t>
-  </si>
-  <si>
     <t>地下水生生物(发光鱿鱼)</t>
   </si>
   <si>
-    <t>WATER_CREATURE</t>
-  </si>
-  <si>
-    <t>WATER_AMBIENT</t>
-  </si>
-  <si>
     <t>水生环境(鳕鱼、鲑鱼、热带鱼、河豚)</t>
   </si>
   <si>
-    <t>MISC</t>
-  </si>
-  <si>
     <t>杂项</t>
   </si>
   <si>
@@ -116,6 +92,38 @@
   </si>
   <si>
     <t>水生生物(鱿鱼、海豚)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>water_creature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>water_ambient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>misc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>underground_water_creature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>axolotls</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ambient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>creature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,190 +468,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.109375" customWidth="1"/>
-    <col min="2" max="2" width="31.88671875" customWidth="1"/>
+    <col min="1" max="1" width="31.08203125" customWidth="1"/>
+    <col min="2" max="2" width="31.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>128</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>128</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>128</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>70</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
+      <c r="B7" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="E7">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>128</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>-1</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9">
+        <v>14</v>
+      </c>
+      <c r="E9">
         <v>128</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
